--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2022_tarapaca.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2022_tarapaca.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29 11:18</t>
+    <t xml:space="preserve">2026-08-19 13:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2022_tarapaca.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2022_tarapaca.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:42</t>
+    <t xml:space="preserve">2026-08-20 12:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2022_tarapaca.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2022_tarapaca.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 12:40</t>
+    <t xml:space="preserve">2026-08-28 15:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -474,13 +474,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>40.95</v>
+        <v>41.38</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>37.51</v>
+        <v>37.97</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
     </row>
   </sheetData>
@@ -583,7 +583,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>81.21</v>
+        <v>81.85</v>
       </c>
     </row>
     <row r="3">
@@ -591,7 +591,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>79.67</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>71.05</v>
+        <v>73.14</v>
       </c>
     </row>
     <row r="5">
@@ -607,7 +607,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>73.71</v>
+        <v>74.95</v>
       </c>
     </row>
     <row r="6">
@@ -615,7 +615,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>79.79</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="7">
@@ -623,7 +623,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>84.44</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="8">
@@ -631,7 +631,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>80.47</v>
+        <v>80.42</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2022_tarapaca.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2022_tarapaca.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:06</t>
+    <t xml:space="preserve">2026-08-29 05:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -474,13 +474,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>41.38</v>
+        <v>82.77</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>37.97</v>
+        <v>75.95</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3.41</v>
+        <v>6.82</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2022_tarapaca.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2022_tarapaca.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:43</t>
+    <t xml:space="preserve">2026-09-07 11:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
